--- a/Dokumentation/Regelkreis Messwerte.xlsx
+++ b/Dokumentation/Regelkreis Messwerte.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\Dokumentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859525C0-9338-4A67-A004-2B6E8192BD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DFA75A-401A-4238-8C7F-6753D928239A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{689FFBA6-619E-4FB9-9DB3-B89793731A5E}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{689FFBA6-619E-4FB9-9DB3-B89793731A5E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Testbedingungen: Sollvorgabe über CAN (zB Dez 50 entspricht 0.5V entspricht 0,5A Ladestrom)</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>Vout in  V</t>
+  </si>
+  <si>
+    <t>Leistung</t>
+  </si>
+  <si>
+    <t>Verlustleistung</t>
   </si>
 </sst>
 </file>
@@ -1214,16 +1220,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>490660</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>40868</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>677904</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>154843</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>490660</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>21818</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>677904</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>135793</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1597,6 +1603,12 @@
       <c r="D4" t="s">
         <v>15</v>
       </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -1611,6 +1623,14 @@
       <c r="D5">
         <v>3.32</v>
       </c>
+      <c r="E5">
+        <f>D5*C5</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>0.25*E5</f>
+        <v>0</v>
+      </c>
       <c r="G5" t="s">
         <v>14</v>
       </c>
@@ -1628,6 +1648,14 @@
       <c r="D6">
         <v>3.34</v>
       </c>
+      <c r="E6">
+        <f t="shared" ref="E6:E18" si="0">D6*C6</f>
+        <v>0.34067999999999998</v>
+      </c>
+      <c r="F6">
+        <f t="shared" ref="F6:F18" si="1">0.25*E6</f>
+        <v>8.5169999999999996E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -1642,6 +1670,14 @@
       <c r="D7">
         <v>3.35</v>
       </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0.67670000000000008</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>0.16917500000000002</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -1656,6 +1692,14 @@
       <c r="D8">
         <v>3.37</v>
       </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>0.25274999999999997</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -1670,6 +1714,14 @@
       <c r="D9">
         <v>3.4</v>
       </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>1.3633999999999999</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>0.34084999999999999</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -1684,6 +1736,14 @@
       <c r="D10">
         <v>3.41</v>
       </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>1.7015900000000002</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>0.42539750000000004</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -1698,6 +1758,14 @@
       <c r="D11">
         <v>3.46</v>
       </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>2.5777000000000001</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>0.64442500000000003</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -1712,6 +1780,14 @@
       <c r="D12">
         <v>3.5</v>
       </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>3.4649999999999999</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>0.86624999999999996</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -1726,6 +1802,14 @@
       <c r="D13">
         <v>3.56</v>
       </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>4.4072800000000001</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>1.10182</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -1740,6 +1824,14 @@
       <c r="D14">
         <v>3.61</v>
       </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>5.3536299999999999</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>1.3384075</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -1754,6 +1846,14 @@
       <c r="D15">
         <v>3.66</v>
       </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>6.3318000000000003</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>1.5829500000000001</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -1768,8 +1868,16 @@
       <c r="D16">
         <v>3.71</v>
       </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>7.3272500000000003</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>1.8318125000000001</v>
+      </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -1782,8 +1890,16 @@
       <c r="D17">
         <v>3.82</v>
       </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>9.4315799999999985</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>2.3578949999999996</v>
+      </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1795,6 +1911,14 @@
       </c>
       <c r="D18">
         <v>3.83</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>9.6477700000000013</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>2.4119425000000003</v>
       </c>
     </row>
   </sheetData>
